--- a/1.training_model/supplementary/dfmergedummydata_withcluster.xlsx
+++ b/1.training_model/supplementary/dfmergedummydata_withcluster.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAC05B6-F09D-4F2F-A63A-2109476A84F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3520" windowWidth="14400" windowHeight="8180" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,23 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1569</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
